--- a/TESTS/zlit_5_penzlyk.xlsx
+++ b/TESTS/zlit_5_penzlyk.xlsx
@@ -507,7 +507,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H46"/>
+  <dimension ref="A1:I46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -561,6 +561,11 @@
           <t>Тип</t>
         </is>
       </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>ГР</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -580,7 +585,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Малян — бідний хлопчик що мріяв малювати і навчитись у майстра</t>
+          <t>Малян</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -601,6 +606,11 @@
       <c r="H2" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -622,7 +632,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Малян мріяв малювати — він тренувався на піску і землі не маючи пензля</t>
+          <t>Малян мріяв малювати</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -643,6 +653,11 @@
       <c r="H3" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -664,7 +679,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Гаряче бажання малювати — він малював скрізь де міг хоч і не мав пензля і паперу</t>
+          <t>Гаряче бажання малювати</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -685,6 +700,11 @@
       <c r="H4" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -706,7 +726,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Старець у сні подарував йому пензлик — нагорода за наполегливість і працелюбність</t>
+          <t>Старець у сні подарував йому пензлик</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -727,6 +747,11 @@
       <c r="H5" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -771,6 +796,11 @@
           <t>single</t>
         </is>
       </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>ГР2</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -790,7 +820,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Все намальоване ним оживає — намалював птаха і птах полетів намалював рибу і риба поплила</t>
+          <t>Все намальоване ним оживає</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -811,6 +841,11 @@
       <c r="H7" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -832,7 +867,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Малював для бідних людей те що їм потрібно — воду плуг тощо — і все це оживало</t>
+          <t>Малював для бідних людей те що їм потрібно</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -853,6 +888,11 @@
       <c r="H8" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -874,7 +914,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Бідним і знедоленим людям — він малював для них те чого вони потребували</t>
+          <t>Бідним і знедоленим людям</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -895,6 +935,11 @@
       <c r="H9" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -916,7 +961,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Будь-що намальоване — птахи летіли риби пливли воли орали поле</t>
+          <t>Будь-що намальоване</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -937,6 +982,11 @@
       <c r="H10" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -948,37 +998,42 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Питання 4 (варіант 1)</t>
+          <t>Чим заробляв на життя Малян до того, як отримав чарівний пензлик?</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Він не працював</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Збирав хмиз і косив траву, бо в родини не було грошей на навчання чи фарби</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Він був багатим купцем</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Він був учнем художника</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -990,37 +1045,42 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Питання 4 (варіант 2)</t>
+          <t>Чим Малян малював, коли не міг дозволити собі пензлик і фарби?</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Він взагалі не малював</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Палицею на піску, вугіллям на стінах — будь-чим, що траплялось під руку</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Купував дешеві матеріали</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Просив у сусідів</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1032,37 +1092,42 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Питання 4 (варіант 3)</t>
+          <t>Чому Малян, попри талант, ніколи не отримував справжнього пензлика від багатих?</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Він не просив</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Бідним людям, як він, ніхто не дарував матеріалів для мистецтва</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Він не хотів пензлика</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Йому забороняли малювати</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1074,37 +1139,42 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Питання 5 (варіант 1)</t>
+          <t>Коли саме до Маляна уві сні з'явився старець із пензликом?</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Зранку після обіду</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Вночі, після того як хлопець заснув, виснажений і сумний, що не має чим малювати</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>У свято</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Під час роботи в полі</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1116,37 +1186,42 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Питання 5 (варіант 2)</t>
+          <t>Що старець сказав Маляну, передаючи пензлик?</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Нічого не сказав</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Що цей пензлик — нагорода за щире серце і наполегливе бажання творити</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Що пензлик треба продати</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Що пензлик можна використати лише раз</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1158,37 +1233,42 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Питання 5 (варіант 3)</t>
+          <t>Як Малян переконався, що пензлик справді чарівний, прокинувшись?</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Він не повірив і відклав його</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Намалював пташку — і вона одразу злетіла з листка живою</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Він спробував його продати</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Пензлик зник, як і уві сні</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1200,37 +1280,42 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Питання 6 (варіант 1)</t>
+          <t>Що Малян намалював для сусіда-селянина, у якого не було плуга?</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Гроші</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Плуг та віл, щоб орати землю</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Будинок</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Одяг</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1242,37 +1327,42 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Питання 6 (варіант 2)</t>
+          <t>Що Малян намалював для бідної родини, в якій не було чим обігрітися взимку?</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Шуба і дрова</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Дрова та теплий одяг</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Гроші на дрова</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Він нічого не намалював, лише пожалів їх</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1284,37 +1374,42 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Питання 6 (варіант 3)</t>
+          <t>Чому Малян ніколи не малював золота чи коштовностей для себе?</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Він боявся покарання</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Йому важливо було допомагати людям у їхніх реальних потребах, а не збагачуватись</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Пензлик не вмів малювати золото</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Йому ніхто не дозволяв</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1326,37 +1421,42 @@
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>Питання 7 (варіант 1)</t>
+          <t>Як новина про чарівний пензлик Маляна дійшла до жадібного мандарина?</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Малян сам похвалився йому</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Чутки про дивовижні малюнки, що оживають, поширились і дійшли до палацу</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Мандарин побачив сам випадково</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Хтось доніс із заздрості</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1368,37 +1468,42 @@
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>Питання 7 (варіант 2)</t>
+          <t>Що мандарин наказав своїм слугам зробити, дізнавшись про Маляна?</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Запросити його у гості</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Схопити хлопця і привести до палацу разом із пензликом</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Дати йому нагороду</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Заборонити малювати</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1410,37 +1515,42 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>Питання 7 (варіант 3)</t>
+          <t>Як Малян почувався, потрапивши до палацу мандарина?</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Радів нагороді</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Розумів, що опинився в небезпеці, бо мандарин — людина жадібна й жорстока</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Йому було байдуже</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Він не зрозумів, що відбувається</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1452,37 +1562,42 @@
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>Питання 8 (варіант 1)</t>
+          <t>Що насамперед наказав намалювати мандарин, опинившись перед Маляном?</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Портрет себе</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Гору золота для своєї скарбниці</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Армію слуг</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Палац для себе</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1494,37 +1609,42 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>Питання 8 (варіант 2)</t>
+          <t>Що насправді намалював Малян замість гори золота, яку просив мандарин?</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Точно те, що просили</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Купу золота, але так, що воно перетворилось на каміння, щойно мандарин до нього торкнувся</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Нічого не намалював</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Малюнок мандарина</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1536,37 +1656,42 @@
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>Питання 8 (варіант 3)</t>
+          <t>Як мандарин відреагував, побачивши, що «золото» перетворилось на каміння?</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Засміявся</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Розгнівався і пригрозив Маляну стратою, якщо той не виконає наказ по-справжньому</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Подякував</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Відпустив Маляна одразу</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1578,37 +1703,42 @@
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>Питання 9 (варіант 1)</t>
+          <t>Що мандарин наказав Маляну намалювати наступного разу, прагнучи дістатися чарівного острова скарбів?</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Літаючий килим</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Великий корабель з повними парусами</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Палац на воді</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Карту острова</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1620,37 +1750,42 @@
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>Питання 9 (варіант 2)</t>
+          <t>Хто сів на корабель, намальований Маляном, разом з мандарином та його родиною?</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Тільки мандарин</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Мандарин, його родина та багато слуг і воїнів</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Лише слуги</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Ніхто, корабель був порожній</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1662,37 +1797,42 @@
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>Питання 9 (варіант 3)</t>
+          <t>Що Малян домалював, коли корабель з мандарином вийшов у відкрите море?</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Острів скарбів</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Сильний вітер і величезні хвилі, що розгойдали корабель</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Інший корабель</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Дельфінів</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1704,37 +1844,42 @@
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>Питання 10 (варіант 1)</t>
+          <t>Що сталося з кораблем мандарина під час намальованого Маляном шторму?</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Він приплив до острова скарбів</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Корабель перекинувся і затонув разом з жадібним мандарином</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Корабель зламався, але всі вижили</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Корабель повернувся назад</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1746,37 +1891,42 @@
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>Питання 10 (варіант 2)</t>
+          <t>Що Малян зробив після того, як урятувався від жадібного мандарина?</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Залишився при дворі новим правителем</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Повернувся до свого села і продовжив допомагати простим людям пензликом</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Сховав пензлик назавжди</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Втік за кордон</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1788,37 +1938,42 @@
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>Питання 10 (варіант 3)</t>
+          <t>Якою рисою Маляна пояснюється те, що чарівний пензлик «послухався» саме його проти мандарина?</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Його силою</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Його кмітливістю і відданістю простим людям, на відміну від жадібності мандарина</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Його багатством</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Випадковістю</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1843,8 +1998,6 @@
           <t>Хибно</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
           <t>Б</t>
@@ -1853,6 +2006,11 @@
       <c r="H32" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1877,8 +2035,6 @@
           <t>Хибно</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
           <t>А</t>
@@ -1887,6 +2043,11 @@
       <c r="H33" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1911,8 +2072,6 @@
           <t>Хибно</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr"/>
-      <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
           <t>Б</t>
@@ -1921,6 +2080,11 @@
       <c r="H34" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1932,21 +2096,19 @@
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>Яке ставлення до мистецтва виражає ця казка?</t>
+          <t>Казка «Пензлик Маляна» виражає думку, що справжнє мистецтво має служити людям, а не збагаченню.</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Так</t>
+          <t>Правда</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Ні</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr"/>
-      <c r="F35" t="inlineStr"/>
+          <t>Хибно</t>
+        </is>
+      </c>
       <c r="G35" t="inlineStr">
         <is>
           <t>А</t>
@@ -1955,6 +2117,11 @@
       <c r="H35" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1966,21 +2133,19 @@
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>До якої країни належить казка «Пензлик Маляна»?</t>
+          <t>«Пензлик Маляна» — китайська народна казка.</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Так</t>
+          <t>Правда</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Ні</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr"/>
-      <c r="F36" t="inlineStr"/>
+          <t>Хибно</t>
+        </is>
+      </c>
       <c r="G36" t="inlineStr">
         <is>
           <t>А</t>
@@ -1989,6 +2154,11 @@
       <c r="H36" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2000,21 +2170,19 @@
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>Яка традиційна китайська цінність відображена в образі Маляна?</t>
+          <t>Образ Маляна втілює традиційну для китайської культури цінність — працьовитість і скромність.</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Так</t>
+          <t>Правда</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Ні</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr"/>
-      <c r="F37" t="inlineStr"/>
+          <t>Хибно</t>
+        </is>
+      </c>
       <c r="G37" t="inlineStr">
         <is>
           <t>А</t>
@@ -2023,6 +2191,11 @@
       <c r="H37" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2034,21 +2207,19 @@
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>Яку хитрість застосував Малян проти жадібного правителя?</t>
+          <t>Проти жадібного мандарина Малян намалював корабель і шторм, що його занапастили.</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Так</t>
+          <t>Правда</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Ні</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr"/>
-      <c r="F38" t="inlineStr"/>
+          <t>Хибно</t>
+        </is>
+      </c>
       <c r="G38" t="inlineStr">
         <is>
           <t>А</t>
@@ -2057,6 +2228,11 @@
       <c r="H38" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2068,29 +2244,32 @@
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>Чим закінчилась казка «Пензлик Маляна»?</t>
+          <t>Казка «Пензлик Маляна» закінчується тим, що хлопець стає новим мандарином.</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Так</t>
+          <t>Правда</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Ні</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr"/>
-      <c r="F39" t="inlineStr"/>
+          <t>Хибно</t>
+        </is>
+      </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2102,21 +2281,19 @@
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>Яка головна думка казки «Пензлик Маляна»?</t>
+          <t>Головна думка казки — талант і чарівна сила повинні служити добру, а не жадібності й несправедливості.</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Так</t>
+          <t>Правда</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Ні</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr"/>
-      <c r="F40" t="inlineStr"/>
+          <t>Хибно</t>
+        </is>
+      </c>
       <c r="G40" t="inlineStr">
         <is>
           <t>А</t>
@@ -2125,6 +2302,11 @@
       <c r="H40" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2169,6 +2351,11 @@
           <t>multiple</t>
         </is>
       </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>ГР2</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2211,6 +2398,11 @@
           <t>multiple</t>
         </is>
       </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>ГР2</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2220,37 +2412,42 @@
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>Які риси характеру Маляна зробили його гідним чарівного пензлика?</t>
+          <t>Як Малян використав свій чарівний пензлик проти жадібного мандарина?</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Наполегливість і працелюбність</t>
+          <t>Намалював золото, що перетворилось на каміння</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Жадібність</t>
+          <t>Намалював корабель</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Доброта до простих людей</t>
+          <t>Домалював шторм, що знищив корабель</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Хитрість проти несправедливих</t>
+          <t>Намалював для мандарина палац</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>А,В,Г</t>
+          <t>А,Б,В</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
           <t>multiple</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2295,6 +2492,11 @@
           <t>multiple</t>
         </is>
       </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>ГР2</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2314,7 +2516,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Малювати незлічимі багатства — гори золота й срібла для задоволення своєї жадібності</t>
+          <t>Малювати незлічимі багатства</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -2335,6 +2537,11 @@
       <c r="H45" t="inlineStr">
         <is>
           <t>multiple</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2356,7 +2563,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Малював хитро — замість прямого виконання він перехитрив мандарина своїми малюнками</t>
+          <t>Малював хитро</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -2377,6 +2584,11 @@
       <c r="H46" t="inlineStr">
         <is>
           <t>multiple</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
